--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82709D9B-8265-46DB-8179-BECD857A3F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483C1B92-A09A-4C8B-8892-72DF6664F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="230">
   <si>
     <t>##var</t>
   </si>
@@ -636,6 +636,199 @@
   </si>
   <si>
     <t>被格挡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.BuffLifetimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeDriven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permanent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯时间倒计时驱动</t>
+  </si>
+  <si>
+    <t>永久被动</t>
+  </si>
+  <si>
+    <t>次数/充能消耗型</t>
+  </si>
+  <si>
+    <t>条件状态依赖型</t>
+  </si>
+  <si>
+    <t>ZZZ.BuffStackBehavior</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff 生命周期类型</t>
+  </si>
+  <si>
+    <t>Buff 叠加与刷新策略</t>
+  </si>
+  <si>
+    <t>叠加层数，并刷新剩余持续时间</t>
+  </si>
+  <si>
+    <t>叠加层数，不刷新持续时间</t>
+  </si>
+  <si>
+    <t>达到上限时拒绝新施加</t>
+  </si>
+  <si>
+    <t>移除旧实例，全新施加</t>
+  </si>
+  <si>
+    <t>独立多实例共存（每层独立计时）</t>
+  </si>
+  <si>
+    <t>ZZZ.BuffEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff 效果类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoRefresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionDriven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChargeCountDriven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RefreshDuration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Independent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PerfectEvade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModifyAttribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invincible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageOverTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealOverTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdControl  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventTrigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性修改（增减攻防、暴击、抗打断）</t>
+  </si>
+  <si>
+    <t>极限闪避（子弹时间、阻断受击）</t>
+  </si>
+  <si>
+    <t>纯无敌（无害免疫）</t>
+  </si>
+  <si>
+    <t>持续伤害 DoT (灼烧/中毒/感电)</t>
+  </si>
+  <si>
+    <t>持续治疗 HoT</t>
+  </si>
+  <si>
+    <t>控制类 (冻结/眩晕/束缚/减速)</t>
+  </si>
+  <si>
+    <t>护盾类 (吸收特定数值伤害)</t>
+  </si>
+  <si>
+    <t>事件触发类 (命中/受击/击杀/闪避后触发衍生效果)</t>
+  </si>
+  <si>
+    <t>ZZZ.BuffTriggerEvent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff 触发事件时机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnBeHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnPerfectEvade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnKill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnShieldBroken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击命中敌人时</t>
+  </si>
+  <si>
+    <t>受到敌人攻击时</t>
+  </si>
+  <si>
+    <t>击杀敌人时</t>
+  </si>
+  <si>
+    <t>护盾破裂时</t>
+  </si>
+  <si>
+    <t>完全由外部手动控制或时间轴片段控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManualDriven</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功触发极限闪避时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1030,13 +1223,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
     <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="23.375" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
@@ -1974,6 +2167,291 @@
         <v>152</v>
       </c>
     </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F75" t="s">
+        <v>184</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H76" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J76">
+        <v>10</v>
+      </c>
+      <c r="K76" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H77" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J77">
+        <v>20</v>
+      </c>
+      <c r="K77" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J78">
+        <v>30</v>
+      </c>
+      <c r="K78" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H79" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J79">
+        <v>40</v>
+      </c>
+      <c r="K79" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B80" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F80" t="s">
+        <v>185</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H81" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J81">
+        <v>10</v>
+      </c>
+      <c r="K81" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H82" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J82">
+        <v>20</v>
+      </c>
+      <c r="K82" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H83" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J83">
+        <v>30</v>
+      </c>
+      <c r="K83" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H84" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J84">
+        <v>40</v>
+      </c>
+      <c r="K84" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H86" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J86">
+        <v>10</v>
+      </c>
+      <c r="K86" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H87" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J87">
+        <v>20</v>
+      </c>
+      <c r="K87" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H88" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J88">
+        <v>30</v>
+      </c>
+      <c r="K88" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H89" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J89">
+        <v>40</v>
+      </c>
+      <c r="K89" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H90" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J90">
+        <v>50</v>
+      </c>
+      <c r="K90" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H91" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J91">
+        <v>60</v>
+      </c>
+      <c r="K91" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H92" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J92">
+        <v>70</v>
+      </c>
+      <c r="K92" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B93" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H94" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J94">
+        <v>10</v>
+      </c>
+      <c r="K94" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H95" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J95">
+        <v>20</v>
+      </c>
+      <c r="K95" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H96" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J96">
+        <v>30</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="97" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H97" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J97">
+        <v>40</v>
+      </c>
+      <c r="K97" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="98" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H98" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J98">
+        <v>50</v>
+      </c>
+      <c r="K98" t="s">
+        <v>226</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483C1B92-A09A-4C8B-8892-72DF6664F099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91B00D4-AF0F-4EA7-99C1-40BEED9917F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="236">
   <si>
     <t>##var</t>
   </si>
@@ -631,10 +631,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Parried </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>被格挡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -829,6 +825,34 @@
   </si>
   <si>
     <t>成功触发极限闪避时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssistPoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxDaze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失衡值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大失衡值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支援点数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parried</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1223,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1447,13 +1471,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H14" s="3" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="J14">
         <v>70</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1853,603 +1877,636 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H49" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J49">
+        <v>300</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H50" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J50">
+        <v>310</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H51" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J51">
+        <v>320</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H52" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J49">
+      <c r="J52">
         <v>2000</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H50" t="s">
-        <v>63</v>
-      </c>
-      <c r="J50">
-        <v>2010</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B51" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" t="s">
-        <v>102</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H52" t="s">
-        <v>93</v>
-      </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H53" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="J53">
-        <v>2</v>
-      </c>
-      <c r="K53" t="s">
-        <v>99</v>
+        <v>2010</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H54" t="s">
-        <v>95</v>
+      <c r="B54" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>102</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H55" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B56" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F56" t="s">
-        <v>107</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>118</v>
+      <c r="H56" t="s">
+        <v>94</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H57" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H58" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B59" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
+      </c>
+      <c r="F59" t="s">
+        <v>107</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="K59" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>108</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>109</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B62" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H60" s="3" t="s">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H63" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J60">
+      <c r="J63">
         <v>1001</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H61" s="3" t="s">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H64" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J61">
+      <c r="J64">
         <v>1002</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="K64" s="3" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H62" s="3" t="s">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H65" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J62">
+      <c r="J65">
         <v>1003</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B63" s="3" t="s">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B66" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J63">
+      <c r="J66">
         <v>0</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H64" t="s">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
         <v>130</v>
       </c>
-      <c r="J64">
+      <c r="J67">
         <v>1</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K67" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H65" t="s">
-        <v>131</v>
-      </c>
-      <c r="J65">
-        <v>2</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H66" t="s">
-        <v>132</v>
-      </c>
-      <c r="J66">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H67" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J67">
-        <v>4</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H68" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B69" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>113</v>
+      <c r="H69" t="s">
+        <v>132</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H70" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H71" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="J71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H72" t="s">
-        <v>144</v>
+      <c r="B72" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H73" t="s">
-        <v>145</v>
+      <c r="H73" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H74" t="s">
+        <v>143</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H75" t="s">
+        <v>144</v>
+      </c>
+      <c r="J75">
+        <v>3</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H76" t="s">
+        <v>145</v>
+      </c>
+      <c r="J76">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H77" t="s">
         <v>146</v>
       </c>
-      <c r="J74">
+      <c r="J77">
         <v>5</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="K77" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B75" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F75" t="s">
-        <v>184</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J75">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B78" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="s">
+        <v>183</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J78">
         <v>0</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H76" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J76">
-        <v>10</v>
-      </c>
-      <c r="K76" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H77" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J77">
-        <v>20</v>
-      </c>
-      <c r="K77" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H78" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J78">
-        <v>30</v>
-      </c>
-      <c r="K78" t="s">
-        <v>181</v>
+      <c r="K78" s="3" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H79" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="J79">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K79" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B80" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F80" t="s">
-        <v>185</v>
-      </c>
       <c r="H80" s="3" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K80" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H81" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J81">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K81" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H82" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J82">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K82" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B83" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" t="s">
+        <v>184</v>
+      </c>
       <c r="H83" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J83">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H84" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J84">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K84" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B85" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="H85" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H86" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J86">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K86" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H87" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J87">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K87" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B88" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="H88" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J88">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H89" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J89">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K89" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H90" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J90">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H91" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J91">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K91" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H92" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J92">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K92" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B93" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="H93" s="3" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="K93" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H94" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="J94">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K94" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H95" s="3" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="J95">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="K95" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B96" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="H96" s="3" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
       <c r="J96">
-        <v>30</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H97" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J97">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K97" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H98" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J98">
+        <v>20</v>
+      </c>
+      <c r="K98" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="99" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H99" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J99">
+        <v>30</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H100" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J100">
+        <v>40</v>
+      </c>
+      <c r="K100" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="101" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H101" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J101">
         <v>50</v>
       </c>
-      <c r="K98" t="s">
-        <v>226</v>
+      <c r="K101" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91B00D4-AF0F-4EA7-99C1-40BEED9917F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B584FBF-9C60-4FC0-9018-BBEFD2B734BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -853,6 +853,22 @@
   </si>
   <si>
     <t>Parried</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PiPie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>派派</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1247,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2081,431 +2097,453 @@
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B66" s="3" t="s">
+      <c r="H66" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J66">
+        <v>1004</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H67" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J67">
+        <v>1005</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B68" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J66">
+      <c r="J68">
         <v>0</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K68" s="3" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H67" t="s">
-        <v>130</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H68" t="s">
-        <v>131</v>
-      </c>
-      <c r="J68">
-        <v>2</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J69">
-        <v>3</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="K69" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H70" s="3" t="s">
-        <v>153</v>
+      <c r="H70" t="s">
+        <v>131</v>
       </c>
       <c r="J70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H71" t="s">
+        <v>132</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H72" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H73" t="s">
         <v>133</v>
       </c>
-      <c r="J71">
+      <c r="J73">
         <v>5</v>
       </c>
-      <c r="K71" s="3" t="s">
+      <c r="K73" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B72" s="3" t="s">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B74" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F74" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="H74" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J72">
+      <c r="J74">
         <v>0</v>
       </c>
-      <c r="K72" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H73" s="3" t="s">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H75" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J73">
+      <c r="J75">
         <v>1</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="K75" s="3" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H74" t="s">
-        <v>143</v>
-      </c>
-      <c r="J74">
-        <v>2</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H75" t="s">
-        <v>144</v>
-      </c>
-      <c r="J75">
-        <v>3</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H76" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H77" t="s">
+        <v>144</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H78" t="s">
+        <v>145</v>
+      </c>
+      <c r="J78">
+        <v>4</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H79" t="s">
         <v>146</v>
       </c>
-      <c r="J77">
+      <c r="J79">
         <v>5</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="K79" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B78" s="3" t="s">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B80" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F80" t="s">
         <v>183</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H80" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="J78">
+      <c r="J80">
         <v>0</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="K80" s="3" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H79" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J79">
-        <v>10</v>
-      </c>
-      <c r="K79" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H80" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J80">
-        <v>20</v>
-      </c>
-      <c r="K80" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H81" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="J81">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K81" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H82" s="3" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="J82">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K82" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B83" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F83" t="s">
-        <v>184</v>
-      </c>
       <c r="H83" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K83" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H84" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J84">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K84" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F85" t="s">
+        <v>184</v>
+      </c>
       <c r="H85" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J85">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H86" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J86">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K86" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H87" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J87">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K87" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B88" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="H88" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K88" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H89" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J89">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K89" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B90" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="H90" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J90">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H91" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J91">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H92" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J92">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H93" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J93">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H94" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J94">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K94" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H95" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J95">
+        <v>50</v>
+      </c>
+      <c r="K95" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H96" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J96">
+        <v>60</v>
+      </c>
+      <c r="K96" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H97" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J95">
+      <c r="J97">
         <v>70</v>
       </c>
-      <c r="K95" t="s">
+      <c r="K97" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B96" s="3" t="s">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B98" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F98" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="H98" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J96">
+      <c r="J98">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H97" s="3" t="s">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H99" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J97">
+      <c r="J99">
         <v>10</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K99" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H98" s="3" t="s">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H100" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="J98">
+      <c r="J100">
         <v>20</v>
       </c>
-      <c r="K98" t="s">
+      <c r="K100" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H99" s="3" t="s">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H101" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J99">
+      <c r="J101">
         <v>30</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H100" s="3" t="s">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H102" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J100">
+      <c r="J102">
         <v>40</v>
       </c>
-      <c r="K100" t="s">
+      <c r="K102" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H101" s="3" t="s">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H103" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J101">
+      <c r="J103">
         <v>50</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K103" t="s">
         <v>225</v>
       </c>
     </row>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B584FBF-9C60-4FC0-9018-BBEFD2B734BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EB64DF-81D3-4975-A1ED-BA13F39DF16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="242">
   <si>
     <t>##var</t>
   </si>
@@ -395,19 +395,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF292929"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ellen_FlashFreeze</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -623,10 +610,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BaseResilience</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>基础抗打断等级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -869,6 +852,19 @@
   </si>
   <si>
     <t>派派</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列1</t>
+  </si>
+  <si>
+    <t>列2</t>
+  </si>
+  <si>
+    <t>列3</t>
+  </si>
+  <si>
+    <t>Resilience</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -876,7 +872,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -900,24 +896,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF292929"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF292929"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF292929"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -934,7 +918,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -957,32 +941,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -992,7 +986,188 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1003,6 +1178,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F449520E-D409-4D96-87E5-6873D755481A}" name="表1" displayName="表1" ref="B3:K103" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+  <autoFilter ref="B3:K103" xr:uid="{F449520E-D409-4D96-87E5-6873D755481A}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4EA0B610-1839-4144-B856-B27AD147EA97}" name="全名(包含模块和名字)" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{E814C035-B74A-433E-BD6B-4A794918CEEF}" name="是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{73706D82-422A-4586-BBC9-E97C86BFB04F}" name="枚举项是否唯一" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{25F48AB7-47C0-422F-9BEA-A5ADD9BB7D81}" name="列1" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{07423DEB-F165-4E1B-88F1-BEC708B39433}" name="列2" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{955976E1-B0E1-4776-B31E-839FF8FEAF9C}" name="列3" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{7BC1A69A-1C0A-40D2-AC22-DBF08CC5814C}" name="枚举名" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{13C67709-0122-457E-A22E-F05E0A335D3B}" name="别名" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{09FD5935-A910-482C-A45A-460C34A89CA0}" name="值" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{68966292-DB66-47B7-992F-931F003224AA}" name="注释" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium28" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1266,13 +1460,14 @@
   <dimension ref="A1:L103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="64.25" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="23.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
+    <col min="7" max="7" width="5.625" customWidth="1"/>
     <col min="8" max="8" width="22.625" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
+    <col min="9" max="9" width="6.5" customWidth="1"/>
     <col min="10" max="10" width="18.625" customWidth="1"/>
     <col min="11" max="11" width="31.375" customWidth="1"/>
   </cols>
@@ -1299,13 +1494,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1337,1214 +1532,1890 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H4" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J4">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J5">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J6">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2">
+        <v>10</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2">
+        <v>20</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
+        <v>30</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2">
+        <v>40</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2">
+        <v>50</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2">
+        <v>60</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2">
+        <v>70</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2">
+        <v>2</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J7">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="J8">
+      <c r="K19" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2">
         <v>10</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9">
+      <c r="K20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2">
         <v>20</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K21" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2">
+        <v>30</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2">
+        <v>40</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2">
+        <v>50</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2">
+        <v>60</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2">
+        <v>70</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2">
+        <v>80</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2">
+        <v>90</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2">
+        <v>100</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2">
+        <v>110</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2">
+        <v>120</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2">
+        <v>130</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2">
+        <v>140</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2">
+        <v>150</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2">
+        <v>160</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2">
         <v>170</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H10" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J10">
+      <c r="K36" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2">
+        <v>180</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2">
+        <v>190</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2">
+        <v>200</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2">
+        <v>210</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2">
+        <v>220</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2">
+        <v>230</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2">
+        <v>240</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2">
+        <v>250</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2">
+        <v>260</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2">
+        <v>270</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2">
+        <v>280</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2">
+        <v>290</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2">
+        <v>300</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2">
+        <v>310</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2">
+        <v>320</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2">
+        <v>2000</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2">
+        <v>2010</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2">
+        <v>1</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2">
+        <v>2</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2">
+        <v>3</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2">
+        <v>4</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2">
+        <v>0</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2">
+        <v>2</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2">
+        <v>0</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2">
+        <v>1001</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2">
+        <v>1002</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2">
+        <v>1003</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2">
+        <v>1004</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2">
+        <v>1005</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B68" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2">
+        <v>1</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2">
+        <v>2</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2">
+        <v>3</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2">
+        <v>4</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2">
+        <v>5</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B74" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2">
+        <v>1</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2">
+        <v>2</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2">
+        <v>3</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2">
+        <v>4</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2">
+        <v>5</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B80" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2">
+        <v>10</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2">
+        <v>20</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2">
         <v>30</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J11">
+      <c r="K83" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2">
         <v>40</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J12">
+      <c r="K84" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2">
+        <v>10</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2">
+        <v>20</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2">
+        <v>30</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2">
+        <v>40</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B90" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2">
+        <v>10</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2">
+        <v>20</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2">
+        <v>30</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2">
+        <v>40</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2">
         <v>50</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J13">
+      <c r="K95" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2">
         <v>60</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J14">
+      <c r="K96" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2">
         <v>70</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" t="s">
+      <c r="K97" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2">
+        <v>0</v>
+      </c>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2">
+        <v>10</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2">
+        <v>20</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2">
         <v>30</v>
       </c>
-      <c r="J16">
-        <v>2</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="F18" s="3"/>
-      <c r="H18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18">
-        <v>2</v>
-      </c>
-      <c r="K18" s="4" t="s">
+      <c r="K101" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20">
-        <v>10</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21">
-        <v>20</v>
-      </c>
-      <c r="K21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J22">
-        <v>30</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H23" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J23">
-        <v>40</v>
-      </c>
-      <c r="K23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24">
+      <c r="K102" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2">
         <v>50</v>
       </c>
-      <c r="K24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H25" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="J25">
-        <v>60</v>
-      </c>
-      <c r="K25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J26">
-        <v>70</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J27">
-        <v>80</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H28" t="s">
-        <v>47</v>
-      </c>
-      <c r="J28">
-        <v>90</v>
-      </c>
-      <c r="K28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H29" t="s">
-        <v>48</v>
-      </c>
-      <c r="J29">
-        <v>100</v>
-      </c>
-      <c r="K29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30">
-        <v>110</v>
-      </c>
-      <c r="K30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J31">
-        <v>120</v>
-      </c>
-      <c r="K31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H32" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32">
-        <v>130</v>
-      </c>
-      <c r="K32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J33">
-        <v>140</v>
-      </c>
-      <c r="K33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F34" s="3"/>
-      <c r="H34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J34">
-        <v>150</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35">
-        <v>160</v>
-      </c>
-      <c r="K35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36">
-        <v>170</v>
-      </c>
-      <c r="K36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J37">
-        <v>180</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J38">
-        <v>190</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H39" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J39">
-        <v>200</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H40" t="s">
-        <v>55</v>
-      </c>
-      <c r="J40">
-        <v>210</v>
-      </c>
-      <c r="K40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H41" t="s">
-        <v>56</v>
-      </c>
-      <c r="J41">
-        <v>220</v>
-      </c>
-      <c r="K41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H42" t="s">
-        <v>57</v>
-      </c>
-      <c r="J42">
-        <v>230</v>
-      </c>
-      <c r="K42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J43">
-        <v>240</v>
-      </c>
-      <c r="K43" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H44" t="s">
-        <v>59</v>
-      </c>
-      <c r="J44">
-        <v>250</v>
-      </c>
-      <c r="K44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H45" t="s">
-        <v>60</v>
-      </c>
-      <c r="J45">
-        <v>260</v>
-      </c>
-      <c r="K45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H46" t="s">
-        <v>61</v>
-      </c>
-      <c r="J46">
-        <v>270</v>
-      </c>
-      <c r="K46" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H47" t="s">
-        <v>62</v>
-      </c>
-      <c r="J47">
-        <v>280</v>
-      </c>
-      <c r="K47" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H48" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J48">
-        <v>290</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H49" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J49">
-        <v>300</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H50" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J50">
-        <v>310</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H51" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J51">
-        <v>320</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H52" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J52">
-        <v>2000</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H53" t="s">
-        <v>63</v>
-      </c>
-      <c r="J53">
-        <v>2010</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B54" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F54" t="s">
-        <v>102</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H55" t="s">
-        <v>93</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
-      <c r="K55" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H56" t="s">
-        <v>94</v>
-      </c>
-      <c r="J56">
-        <v>2</v>
-      </c>
-      <c r="K56" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H57" t="s">
-        <v>95</v>
-      </c>
-      <c r="J57">
-        <v>3</v>
-      </c>
-      <c r="K57" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H58" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58">
-        <v>4</v>
-      </c>
-      <c r="K58" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B59" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F59" t="s">
-        <v>107</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H60" t="s">
-        <v>108</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J61">
-        <v>2</v>
-      </c>
-      <c r="K61" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B62" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H63" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J63">
-        <v>1001</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H64" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J64">
-        <v>1002</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H65" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J65">
-        <v>1003</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H66" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J66">
-        <v>1004</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H67" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J67">
-        <v>1005</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B68" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H69" t="s">
-        <v>130</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H70" t="s">
-        <v>131</v>
-      </c>
-      <c r="J70">
-        <v>2</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H71" t="s">
-        <v>132</v>
-      </c>
-      <c r="J71">
-        <v>3</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H72" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J72">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H73" t="s">
-        <v>133</v>
-      </c>
-      <c r="J73">
-        <v>5</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B74" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H75" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H76" t="s">
-        <v>143</v>
-      </c>
-      <c r="J76">
-        <v>2</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H77" t="s">
-        <v>144</v>
-      </c>
-      <c r="J77">
-        <v>3</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H78" t="s">
-        <v>145</v>
-      </c>
-      <c r="J78">
-        <v>4</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H79" t="s">
-        <v>146</v>
-      </c>
-      <c r="J79">
-        <v>5</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B80" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" t="s">
-        <v>183</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H81" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J81">
-        <v>10</v>
-      </c>
-      <c r="K81" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H82" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J82">
-        <v>20</v>
-      </c>
-      <c r="K82" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H83" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J83">
-        <v>30</v>
-      </c>
-      <c r="K83" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H84" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J84">
-        <v>40</v>
-      </c>
-      <c r="K84" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B85" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F85" t="s">
-        <v>184</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H86" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J86">
-        <v>10</v>
-      </c>
-      <c r="K86" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H87" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J87">
-        <v>20</v>
-      </c>
-      <c r="K87" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H88" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J88">
-        <v>30</v>
-      </c>
-      <c r="K88" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H89" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J89">
-        <v>40</v>
-      </c>
-      <c r="K89" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B90" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H91" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J91">
-        <v>10</v>
-      </c>
-      <c r="K91" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H92" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J92">
-        <v>20</v>
-      </c>
-      <c r="K92" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H93" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="J93">
-        <v>30</v>
-      </c>
-      <c r="K93" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H94" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J94">
-        <v>40</v>
-      </c>
-      <c r="K94" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H95" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J95">
-        <v>50</v>
-      </c>
-      <c r="K95" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H96" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J96">
-        <v>60</v>
-      </c>
-      <c r="K96" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H97" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="J97">
-        <v>70</v>
-      </c>
-      <c r="K97" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B98" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H99" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J99">
-        <v>10</v>
-      </c>
-      <c r="K99" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H100" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J100">
-        <v>20</v>
-      </c>
-      <c r="K100" t="s">
+      <c r="K103" s="2" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H101" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J101">
-        <v>30</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H102" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J102">
-        <v>40</v>
-      </c>
-      <c r="K102" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H103" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J103">
-        <v>50</v>
-      </c>
-      <c r="K103" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -2554,5 +3425,8 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>